--- a/Docs/Test Docs/Conslidated Financial Plan.xlsx
+++ b/Docs/Test Docs/Conslidated Financial Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\subashcse009-bit\MyMoneyMate\Docs\Test Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F487D870-D61F-49A8-B551-1DB4C83CE3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEE0252-DD64-4151-B295-0E62FE436F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>Office</t>
   </si>
   <si>
-    <t>Credit Card</t>
-  </si>
-  <si>
     <t>Sarah</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>Income Amount</t>
   </si>
   <si>
-    <t>Daily Exp</t>
-  </si>
-  <si>
     <t>Account Transfer</t>
   </si>
   <si>
@@ -359,9 +353,6 @@
     <t>Ornamental Fish Trade Center</t>
   </si>
   <si>
-    <t>Credit Card Bill</t>
-  </si>
-  <si>
     <t>Sahve</t>
   </si>
   <si>
@@ -573,6 +564,15 @@
   </si>
   <si>
     <t>Subash</t>
+  </si>
+  <si>
+    <t>HDFC Credit Card</t>
+  </si>
+  <si>
+    <t>HDFC Credit Card Bill</t>
+  </si>
+  <si>
+    <t>Daily Expense</t>
   </si>
 </sst>
 </file>
@@ -987,22 +987,22 @@
         <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1013,7 +1013,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -1026,13 +1026,13 @@
         <v>46250</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -1053,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -1071,7 +1071,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -1089,7 +1089,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -1107,7 +1107,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1128,10 +1128,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -1164,7 +1164,7 @@
         <v>46247</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -1185,13 +1185,13 @@
         <v>46247</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -1209,10 +1209,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -1245,13 +1245,13 @@
         <v>46246</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -1266,13 +1266,13 @@
         <v>46246</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -1290,10 +1290,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -1308,7 +1308,7 @@
         <v>46245</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1326,13 +1326,13 @@
         <v>46245</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -1347,13 +1347,13 @@
         <v>46245</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -1368,13 +1368,13 @@
         <v>46245</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -1389,10 +1389,10 @@
         <v>46244</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -1410,7 +1410,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -1428,7 +1428,7 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
@@ -1449,10 +1449,10 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -1470,7 +1470,7 @@
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -1491,7 +1491,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -1506,13 +1506,13 @@
         <v>46243</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -1527,10 +1527,10 @@
         <v>46243</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -1548,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -1563,13 +1563,13 @@
         <v>46242</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C30" t="s">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -1590,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -1605,10 +1605,10 @@
         <v>46242</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -1623,10 +1623,10 @@
         <v>46242</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -1641,13 +1641,13 @@
         <v>46242</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -1665,10 +1665,10 @@
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E35" t="s">
         <v>17</v>
@@ -1686,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -1704,7 +1704,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -1719,10 +1719,10 @@
         <v>46241</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -1740,7 +1740,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -1758,7 +1758,7 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -1776,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
@@ -1794,7 +1794,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -1809,13 +1809,13 @@
         <v>46240</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -1833,10 +1833,10 @@
         <v>19</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -1854,7 +1854,7 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -1872,10 +1872,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -1890,13 +1890,13 @@
         <v>46239</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -1947,10 +1947,10 @@
         <v>46239</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -1968,7 +1968,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -1986,7 +1986,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -2001,13 +2001,13 @@
         <v>46238</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
@@ -2022,13 +2022,13 @@
         <v>46238</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
@@ -2046,7 +2046,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E55" t="s">
         <v>17</v>
@@ -2061,13 +2061,13 @@
         <v>46238</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -2082,10 +2082,10 @@
         <v>46238</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -2103,7 +2103,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -2118,10 +2118,10 @@
         <v>46238</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -2136,10 +2136,10 @@
         <v>46238</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
         <v>17</v>
@@ -2157,7 +2157,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
@@ -2175,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -2196,7 +2196,7 @@
         <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
@@ -2214,7 +2214,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E64" t="s">
         <v>17</v>
@@ -2247,13 +2247,13 @@
         <v>46237</v>
       </c>
       <c r="B66" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
         <v>17</v>
@@ -2268,13 +2268,13 @@
         <v>46237</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
@@ -2289,13 +2289,13 @@
         <v>46237</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E68" t="s">
         <v>17</v>
@@ -2313,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
@@ -2331,7 +2331,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
         <v>17</v>
@@ -2346,7 +2346,7 @@
         <v>46236</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -2364,13 +2364,13 @@
         <v>46236</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -2385,13 +2385,13 @@
         <v>46235</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E73" t="s">
         <v>17</v>
@@ -2406,13 +2406,13 @@
         <v>46235</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C74" t="s">
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -2427,13 +2427,13 @@
         <v>46235</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
       </c>
       <c r="D75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
@@ -2448,10 +2448,10 @@
         <v>46235</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -2469,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D77" t="s">
         <v>10</v>
@@ -2487,10 +2487,10 @@
         <v>46235</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E78" t="s">
         <v>17</v>
@@ -2508,7 +2508,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
@@ -2526,10 +2526,10 @@
         <v>16</v>
       </c>
       <c r="C80" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D80" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -2562,10 +2562,10 @@
         <v>46235</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E82" t="s">
         <v>17</v>
@@ -2580,10 +2580,10 @@
         <v>46234</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E83" t="s">
         <v>17</v>
@@ -2601,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
@@ -2622,7 +2622,7 @@
         <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
@@ -2637,13 +2637,13 @@
         <v>46233</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
@@ -2658,13 +2658,13 @@
         <v>46233</v>
       </c>
       <c r="B87" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C87" t="s">
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
@@ -2679,10 +2679,10 @@
         <v>46233</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -2700,7 +2700,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -2715,13 +2715,13 @@
         <v>46232</v>
       </c>
       <c r="B90" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -2736,7 +2736,7 @@
         <v>46230</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -2760,7 +2760,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -2778,7 +2778,7 @@
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D93" t="s">
         <v>10</v>
@@ -2802,7 +2802,7 @@
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E94" t="s">
         <v>17</v>
@@ -2823,7 +2823,7 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E95" t="s">
         <v>17</v>
@@ -2844,7 +2844,7 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
@@ -2859,13 +2859,13 @@
         <v>46228</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
@@ -2880,13 +2880,13 @@
         <v>46227</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
@@ -2907,7 +2907,7 @@
         <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
@@ -2922,13 +2922,13 @@
         <v>46227</v>
       </c>
       <c r="B100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -2943,13 +2943,13 @@
         <v>46226</v>
       </c>
       <c r="B101" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C101" t="s">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -2964,7 +2964,7 @@
         <v>46226</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -2988,7 +2988,7 @@
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E103" t="s">
         <v>17</v>
@@ -3003,13 +3003,13 @@
         <v>46225</v>
       </c>
       <c r="B104" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E104" t="s">
         <v>17</v>
@@ -3027,7 +3027,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E105" t="s">
         <v>17</v>
@@ -3045,7 +3045,7 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E106" t="s">
         <v>17</v>
@@ -3063,10 +3063,10 @@
         <v>16</v>
       </c>
       <c r="C107" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E107" t="s">
         <v>17</v>
@@ -3081,13 +3081,13 @@
         <v>46223</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C108" t="s">
         <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E108" t="s">
         <v>17</v>
@@ -3105,10 +3105,10 @@
         <v>19</v>
       </c>
       <c r="C109" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D109" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E109" t="s">
         <v>17</v>
@@ -3123,13 +3123,13 @@
         <v>46222</v>
       </c>
       <c r="B110" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D110" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E110" t="s">
         <v>17</v>
@@ -3144,13 +3144,13 @@
         <v>46222</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C111" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D111" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E111" t="s">
         <v>17</v>
@@ -3165,13 +3165,13 @@
         <v>46221</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C112" t="s">
         <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E112" t="s">
         <v>17</v>
@@ -3186,7 +3186,7 @@
         <v>46221</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C113" t="s">
         <v>12</v>
@@ -3204,13 +3204,13 @@
         <v>46220</v>
       </c>
       <c r="B114" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D114" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E114" t="s">
         <v>17</v>
@@ -3231,7 +3231,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E115" t="s">
         <v>17</v>
@@ -3246,13 +3246,13 @@
         <v>46218</v>
       </c>
       <c r="B116" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C116" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D116" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E116" t="s">
         <v>17</v>
@@ -3270,10 +3270,10 @@
         <v>16</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D117" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E117" t="s">
         <v>17</v>
@@ -3288,10 +3288,10 @@
         <v>46217</v>
       </c>
       <c r="B118" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C118" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E118" t="s">
         <v>17</v>
@@ -3306,10 +3306,10 @@
         <v>46216</v>
       </c>
       <c r="B119" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C119" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E119" t="s">
         <v>17</v>
@@ -3327,7 +3327,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E120" t="s">
         <v>17</v>
@@ -3342,13 +3342,13 @@
         <v>46215</v>
       </c>
       <c r="B121" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E121" t="s">
         <v>17</v>
@@ -3363,13 +3363,13 @@
         <v>46215</v>
       </c>
       <c r="B122" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E122" t="s">
         <v>17</v>
@@ -3384,7 +3384,7 @@
         <v>46215</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C123" t="s">
         <v>12</v>
@@ -3402,13 +3402,13 @@
         <v>46215</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C124" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E124" t="s">
         <v>17</v>
@@ -3426,7 +3426,7 @@
         <v>19</v>
       </c>
       <c r="C125" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D125" t="s">
         <v>10</v>
@@ -3444,13 +3444,13 @@
         <v>46214</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C126" t="s">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E126" t="s">
         <v>17</v>
@@ -3468,7 +3468,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D127" t="s">
         <v>8</v>
@@ -3489,10 +3489,10 @@
         <v>19</v>
       </c>
       <c r="C128" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D128" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E128" t="s">
         <v>17</v>
@@ -3507,10 +3507,10 @@
         <v>46213</v>
       </c>
       <c r="B129" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E129" t="s">
         <v>17</v>
@@ -3528,7 +3528,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E130" t="s">
         <v>17</v>
@@ -3546,7 +3546,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E131" t="s">
         <v>17</v>
@@ -3567,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E132" t="s">
         <v>17</v>
@@ -3582,10 +3582,10 @@
         <v>46212</v>
       </c>
       <c r="B133" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E133" t="s">
         <v>17</v>
@@ -3603,7 +3603,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E134" t="s">
         <v>17</v>
@@ -3618,13 +3618,13 @@
         <v>46211</v>
       </c>
       <c r="B135" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C135" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D135" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E135" t="s">
         <v>17</v>
@@ -3639,10 +3639,10 @@
         <v>46211</v>
       </c>
       <c r="B136" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C136" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E136" t="s">
         <v>17</v>
@@ -3657,10 +3657,10 @@
         <v>46211</v>
       </c>
       <c r="B137" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E137" t="s">
         <v>17</v>
@@ -3675,13 +3675,13 @@
         <v>46211</v>
       </c>
       <c r="B138" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C138" t="s">
         <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E138" t="s">
         <v>17</v>
@@ -3696,7 +3696,7 @@
         <v>46211</v>
       </c>
       <c r="B139" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C139" t="s">
         <v>12</v>
@@ -3717,10 +3717,10 @@
         <v>16</v>
       </c>
       <c r="C140" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D140" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E140" t="s">
         <v>17</v>
@@ -3738,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="C141" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -3759,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E142" t="s">
         <v>17</v>
@@ -3777,7 +3777,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E143" t="s">
         <v>17</v>
@@ -3795,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="C144" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E144" t="s">
         <v>17</v>
@@ -3813,7 +3813,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E145" t="s">
         <v>17</v>
@@ -3831,7 +3831,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E146" t="s">
         <v>17</v>
@@ -3846,13 +3846,13 @@
         <v>46209</v>
       </c>
       <c r="B147" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C147" t="s">
         <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E147" t="s">
         <v>17</v>
@@ -3870,7 +3870,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E148" t="s">
         <v>17</v>
@@ -3885,10 +3885,10 @@
         <v>46208</v>
       </c>
       <c r="B149" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C149" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E149" t="s">
         <v>17</v>
@@ -3906,7 +3906,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E150" t="s">
         <v>17</v>
@@ -3924,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E151" t="s">
         <v>17</v>
@@ -3939,13 +3939,13 @@
         <v>46208</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C152" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D152" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E152" t="s">
         <v>17</v>
@@ -3960,7 +3960,7 @@
         <v>46208</v>
       </c>
       <c r="B153" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C153" t="s">
         <v>12</v>
@@ -3981,7 +3981,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -4023,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E156" t="s">
         <v>17</v>
@@ -4038,10 +4038,10 @@
         <v>46207</v>
       </c>
       <c r="B157" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C157" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E157" t="s">
         <v>17</v>
@@ -4059,7 +4059,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E158" t="s">
         <v>17</v>
@@ -4074,13 +4074,13 @@
         <v>46207</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C159" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D159" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E159" t="s">
         <v>17</v>
@@ -4095,10 +4095,10 @@
         <v>46207</v>
       </c>
       <c r="B160" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C160" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E160" t="s">
         <v>17</v>
@@ -4113,10 +4113,10 @@
         <v>46207</v>
       </c>
       <c r="B161" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C161" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E161" t="s">
         <v>17</v>
@@ -4131,10 +4131,10 @@
         <v>46206</v>
       </c>
       <c r="B162" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C162" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E162" t="s">
         <v>17</v>
@@ -4152,7 +4152,7 @@
         <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E163" t="s">
         <v>17</v>
@@ -4170,7 +4170,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E164" t="s">
         <v>17</v>
@@ -4206,7 +4206,7 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E166" t="s">
         <v>17</v>
@@ -4224,7 +4224,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E167" t="s">
         <v>17</v>
@@ -4245,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="D168" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E168" t="s">
         <v>17</v>
@@ -4260,13 +4260,13 @@
         <v>46204</v>
       </c>
       <c r="B169" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E169" t="s">
         <v>17</v>
@@ -4281,7 +4281,7 @@
         <v>46204</v>
       </c>
       <c r="B170" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C170" t="s">
         <v>12</v>
@@ -4305,7 +4305,7 @@
         <v>4</v>
       </c>
       <c r="D171" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E171" t="s">
         <v>17</v>
@@ -4323,7 +4323,7 @@
         <v>19</v>
       </c>
       <c r="C172" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -4344,7 +4344,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E173" t="s">
         <v>17</v>
@@ -4380,10 +4380,10 @@
         <v>46204</v>
       </c>
       <c r="B175" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C175" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E175" t="s">
         <v>17</v>
@@ -4401,7 +4401,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E176" t="s">
         <v>17</v>
@@ -4419,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D177" t="s">
         <v>10</v>
@@ -4440,10 +4440,10 @@
         <v>16</v>
       </c>
       <c r="C178" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D178" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E178" t="s">
         <v>17</v>
@@ -4479,10 +4479,10 @@
         <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D180" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E180" t="s">
         <v>17</v>
@@ -4500,7 +4500,7 @@
         <v>19</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E181" t="s">
         <v>19</v>
@@ -4518,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E182" t="s">
         <v>17</v>
@@ -4554,10 +4554,10 @@
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D184" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E184" t="s">
         <v>17</v>
@@ -4575,10 +4575,10 @@
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D185" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E185" t="s">
         <v>17</v>
@@ -4593,10 +4593,10 @@
         <v>46204</v>
       </c>
       <c r="B186" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C186" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E186" t="s">
         <v>17</v>
@@ -4611,13 +4611,13 @@
         <v>46203</v>
       </c>
       <c r="B187" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C187" t="s">
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E187" t="s">
         <v>17</v>
@@ -4632,16 +4632,16 @@
         <v>46203</v>
       </c>
       <c r="B188" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C188" t="s">
         <v>13</v>
       </c>
       <c r="D188" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E188" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F188" s="5">
         <v>48</v>
@@ -4653,10 +4653,10 @@
         <v>46203</v>
       </c>
       <c r="B189" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E189" t="s">
         <v>17</v>
@@ -4671,10 +4671,10 @@
         <v>46203</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C190" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E190" t="s">
         <v>17</v>
@@ -4692,7 +4692,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E191" t="s">
         <v>17</v>
@@ -4710,7 +4710,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E192" t="s">
         <v>17</v>
@@ -4725,16 +4725,16 @@
         <v>46202</v>
       </c>
       <c r="B193" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C193" t="s">
         <v>13</v>
       </c>
       <c r="D193" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E193" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F193" s="5">
         <v>48</v>
@@ -4746,13 +4746,13 @@
         <v>46201</v>
       </c>
       <c r="B194" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C194" t="s">
         <v>12</v>
       </c>
       <c r="E194" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F194" s="5">
         <v>290</v>
@@ -4764,16 +4764,16 @@
         <v>46201</v>
       </c>
       <c r="B195" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C195" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D195" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E195" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F195" s="5">
         <v>245</v>
@@ -4785,13 +4785,13 @@
         <v>46199</v>
       </c>
       <c r="B196" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D196" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E196" t="s">
         <v>17</v>
@@ -4806,16 +4806,16 @@
         <v>46199</v>
       </c>
       <c r="B197" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C197" t="s">
         <v>13</v>
       </c>
       <c r="D197" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E197" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F197" s="5">
         <v>131</v>
@@ -4827,13 +4827,13 @@
         <v>46199</v>
       </c>
       <c r="B198" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C198" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E198" t="s">
         <v>17</v>
@@ -4848,16 +4848,16 @@
         <v>46199</v>
       </c>
       <c r="B199" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C199" t="s">
         <v>13</v>
       </c>
       <c r="D199" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E199" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F199" s="5">
         <v>100</v>
@@ -4869,16 +4869,16 @@
         <v>46198</v>
       </c>
       <c r="B200" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C200" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D200" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E200" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F200" s="5">
         <v>235</v>
@@ -4890,16 +4890,16 @@
         <v>46198</v>
       </c>
       <c r="B201" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C201" t="s">
         <v>3</v>
       </c>
       <c r="D201" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E201" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F201" s="5">
         <v>124</v>
@@ -4911,16 +4911,16 @@
         <v>46197</v>
       </c>
       <c r="B202" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C202" t="s">
         <v>12</v>
       </c>
       <c r="D202" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E202" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F202" s="5">
         <v>290</v>
@@ -4932,13 +4932,13 @@
         <v>46195</v>
       </c>
       <c r="B203" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C203" t="s">
         <v>13</v>
       </c>
       <c r="D203" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E203" t="s">
         <v>17</v>
@@ -4953,13 +4953,13 @@
         <v>46195</v>
       </c>
       <c r="B204" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C204" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D204" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E204" t="s">
         <v>17</v>
@@ -4974,13 +4974,13 @@
         <v>46195</v>
       </c>
       <c r="B205" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C205" t="s">
         <v>14</v>
       </c>
       <c r="D205" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E205" t="s">
         <v>17</v>
@@ -4998,7 +4998,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D206" t="s">
         <v>27</v>
@@ -5019,10 +5019,10 @@
         <v>19</v>
       </c>
       <c r="C207" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D207" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E207" t="s">
         <v>19</v>
@@ -5037,16 +5037,16 @@
         <v>46194</v>
       </c>
       <c r="B208" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C208" t="s">
         <v>12</v>
       </c>
       <c r="D208" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E208" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F208" s="5">
         <v>290</v>
@@ -5058,16 +5058,16 @@
         <v>46194</v>
       </c>
       <c r="B209" t="s">
+        <v>42</v>
+      </c>
+      <c r="C209" t="s">
+        <v>109</v>
+      </c>
+      <c r="D209" t="s">
+        <v>119</v>
+      </c>
+      <c r="E209" t="s">
         <v>44</v>
-      </c>
-      <c r="C209" t="s">
-        <v>112</v>
-      </c>
-      <c r="D209" t="s">
-        <v>122</v>
-      </c>
-      <c r="E209" t="s">
-        <v>46</v>
       </c>
       <c r="F209" s="5">
         <v>553</v>
@@ -5085,10 +5085,10 @@
         <v>3</v>
       </c>
       <c r="D210" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E210" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F210" s="5">
         <v>1050</v>
@@ -5100,16 +5100,16 @@
         <v>46193</v>
       </c>
       <c r="B211" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C211" t="s">
         <v>3</v>
       </c>
       <c r="D211" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E211" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F211" s="5">
         <v>900</v>
@@ -5142,16 +5142,16 @@
         <v>46192</v>
       </c>
       <c r="B213" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C213" t="s">
         <v>3</v>
       </c>
       <c r="D213" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E213" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F213" s="5">
         <v>500</v>
@@ -5163,16 +5163,16 @@
         <v>46192</v>
       </c>
       <c r="B214" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C214" t="s">
         <v>3</v>
       </c>
       <c r="D214" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E214" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F214" s="5">
         <v>900</v>
@@ -5184,16 +5184,16 @@
         <v>46191</v>
       </c>
       <c r="B215" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C215" t="s">
         <v>3</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E215" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F215" s="5">
         <v>220</v>
@@ -5211,7 +5211,7 @@
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E216" t="s">
         <v>20</v>
@@ -5229,10 +5229,10 @@
         <v>19</v>
       </c>
       <c r="C217" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D217" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E217" t="s">
         <v>19</v>
@@ -5247,16 +5247,16 @@
         <v>46189</v>
       </c>
       <c r="B218" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C218" t="s">
         <v>13</v>
       </c>
       <c r="D218" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E218" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F218" s="5">
         <v>48</v>
@@ -5268,16 +5268,16 @@
         <v>46188</v>
       </c>
       <c r="B219" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C219" t="s">
         <v>21</v>
       </c>
       <c r="D219" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E219" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F219" s="5">
         <v>1468</v>
@@ -5289,16 +5289,16 @@
         <v>46188</v>
       </c>
       <c r="B220" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C220" t="s">
         <v>12</v>
       </c>
       <c r="D220" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E220" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F220" s="5">
         <v>290</v>
@@ -5310,16 +5310,16 @@
         <v>46188</v>
       </c>
       <c r="B221" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C221" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D221" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E221" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F221" s="5">
         <v>319</v>
@@ -5334,7 +5334,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D222" t="s">
         <v>26</v>
@@ -5352,16 +5352,16 @@
         <v>46187</v>
       </c>
       <c r="B223" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C223" t="s">
         <v>3</v>
       </c>
       <c r="D223" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E223" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F223" s="5">
         <v>2188.5</v>
@@ -5376,10 +5376,10 @@
         <v>19</v>
       </c>
       <c r="C224" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D224" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E224" t="s">
         <v>17</v>
@@ -5394,16 +5394,16 @@
         <v>46186</v>
       </c>
       <c r="B225" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C225" t="s">
         <v>21</v>
       </c>
       <c r="D225" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E225" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F225" s="5">
         <v>2203</v>
@@ -5415,16 +5415,16 @@
         <v>46184</v>
       </c>
       <c r="B226" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C226" t="s">
         <v>12</v>
       </c>
       <c r="D226" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E226" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F226" s="5">
         <v>290</v>
@@ -5436,13 +5436,13 @@
         <v>46184</v>
       </c>
       <c r="B227" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C227" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D227" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E227" t="s">
         <v>17</v>
@@ -5460,7 +5460,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D228" t="s">
         <v>25</v>
@@ -5478,10 +5478,10 @@
         <v>46184</v>
       </c>
       <c r="B229" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C229" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E229" t="s">
         <v>17</v>
@@ -5499,7 +5499,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E230" t="s">
         <v>17</v>
@@ -5514,10 +5514,10 @@
         <v>46184</v>
       </c>
       <c r="B231" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C231" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E231" t="s">
         <v>17</v>
@@ -5535,7 +5535,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E232" t="s">
         <v>17</v>
@@ -5550,7 +5550,7 @@
         <v>46183</v>
       </c>
       <c r="B233" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C233" t="s">
         <v>13</v>
@@ -5574,7 +5574,7 @@
         <v>3</v>
       </c>
       <c r="D234" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E234" t="s">
         <v>17</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="D235" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E235" t="s">
         <v>17</v>
@@ -5613,10 +5613,10 @@
         <v>19</v>
       </c>
       <c r="C236" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D236" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E236" t="s">
         <v>19</v>
@@ -5631,10 +5631,10 @@
         <v>46183</v>
       </c>
       <c r="B237" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C237" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E237" t="s">
         <v>17</v>
@@ -5649,10 +5649,10 @@
         <v>46183</v>
       </c>
       <c r="B238" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C238" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E238" t="s">
         <v>17</v>
@@ -5670,7 +5670,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E239" t="s">
         <v>17</v>
@@ -5688,7 +5688,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E240" t="s">
         <v>17</v>
@@ -5706,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E241" t="s">
         <v>17</v>
@@ -5721,10 +5721,10 @@
         <v>46182</v>
       </c>
       <c r="B242" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C242" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E242" t="s">
         <v>17</v>
@@ -5739,10 +5739,10 @@
         <v>46182</v>
       </c>
       <c r="B243" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C243" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E243" t="s">
         <v>17</v>
@@ -5760,7 +5760,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E244" t="s">
         <v>17</v>
@@ -5781,7 +5781,7 @@
         <v>3</v>
       </c>
       <c r="D245" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E245" t="s">
         <v>17</v>
@@ -5796,16 +5796,16 @@
         <v>46181</v>
       </c>
       <c r="B246" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C246" t="s">
         <v>12</v>
       </c>
       <c r="D246" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E246" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F246" s="5">
         <v>290</v>
@@ -5817,10 +5817,10 @@
         <v>46181</v>
       </c>
       <c r="B247" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C247" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E247" t="s">
         <v>17</v>
@@ -5835,10 +5835,10 @@
         <v>46181</v>
       </c>
       <c r="B248" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C248" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E248" t="s">
         <v>17</v>
@@ -5853,10 +5853,10 @@
         <v>46181</v>
       </c>
       <c r="B249" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C249" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E249" t="s">
         <v>17</v>
@@ -5874,7 +5874,7 @@
         <v>6</v>
       </c>
       <c r="C250" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -5895,7 +5895,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E251" t="s">
         <v>17</v>
@@ -5913,7 +5913,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E252" t="s">
         <v>17</v>
@@ -5931,10 +5931,10 @@
         <v>19</v>
       </c>
       <c r="C253" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D253" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E253" t="s">
         <v>19</v>
@@ -5955,7 +5955,7 @@
         <v>4</v>
       </c>
       <c r="D254" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E254" t="s">
         <v>19</v>
@@ -5973,10 +5973,10 @@
         <v>19</v>
       </c>
       <c r="C255" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D255" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E255" t="s">
         <v>17</v>
@@ -5994,7 +5994,7 @@
         <v>6</v>
       </c>
       <c r="C256" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E256" t="s">
         <v>17</v>
@@ -6012,7 +6012,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E257" t="s">
         <v>17</v>
@@ -6030,7 +6030,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E258" t="s">
         <v>17</v>
@@ -6045,16 +6045,16 @@
         <v>46179</v>
       </c>
       <c r="B259" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C259" t="s">
         <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E259" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F259" s="5">
         <v>440</v>
@@ -6069,7 +6069,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E260" t="s">
         <v>17</v>
@@ -6084,10 +6084,10 @@
         <v>46178</v>
       </c>
       <c r="B261" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C261" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E261" t="s">
         <v>17</v>
@@ -6102,10 +6102,10 @@
         <v>46178</v>
       </c>
       <c r="B262" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C262" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E262" t="s">
         <v>17</v>
@@ -6123,7 +6123,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E263" t="s">
         <v>17</v>
@@ -6141,7 +6141,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E264" t="s">
         <v>17</v>
@@ -6156,13 +6156,13 @@
         <v>46178</v>
       </c>
       <c r="B265" t="s">
+        <v>42</v>
+      </c>
+      <c r="C265" t="s">
+        <v>109</v>
+      </c>
+      <c r="E265" t="s">
         <v>44</v>
-      </c>
-      <c r="C265" t="s">
-        <v>112</v>
-      </c>
-      <c r="E265" t="s">
-        <v>46</v>
       </c>
       <c r="F265" s="5">
         <v>1540.87</v>
@@ -6174,13 +6174,13 @@
         <v>46178</v>
       </c>
       <c r="B266" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C266" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D266" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E266" t="s">
         <v>17</v>
@@ -6195,13 +6195,13 @@
         <v>46178</v>
       </c>
       <c r="B267" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C267" t="s">
         <v>12</v>
       </c>
       <c r="D267" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E267" t="s">
         <v>17</v>
@@ -6219,10 +6219,10 @@
         <v>19</v>
       </c>
       <c r="C268" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D268" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E268" t="s">
         <v>17</v>
@@ -6240,7 +6240,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E269" t="s">
         <v>17</v>
@@ -6255,10 +6255,10 @@
         <v>46177</v>
       </c>
       <c r="B270" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C270" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E270" t="s">
         <v>17</v>
@@ -6273,10 +6273,10 @@
         <v>46177</v>
       </c>
       <c r="B271" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C271" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E271" t="s">
         <v>17</v>
@@ -6294,7 +6294,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E272" t="s">
         <v>17</v>
@@ -6309,10 +6309,10 @@
         <v>46177</v>
       </c>
       <c r="B273" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C273" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E273" t="s">
         <v>17</v>
@@ -6327,10 +6327,10 @@
         <v>46177</v>
       </c>
       <c r="B274" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C274" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E274" t="s">
         <v>17</v>
@@ -6345,10 +6345,10 @@
         <v>46177</v>
       </c>
       <c r="B275" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C275" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E275" t="s">
         <v>17</v>
@@ -6363,13 +6363,13 @@
         <v>46176</v>
       </c>
       <c r="B276" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C276" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D276" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E276" t="s">
         <v>17</v>
@@ -6387,7 +6387,7 @@
         <v>19</v>
       </c>
       <c r="C277" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D277" t="s">
         <v>28</v>
@@ -6408,7 +6408,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D278" t="s">
         <v>28</v>
@@ -6429,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D279" t="s">
         <v>18</v>
@@ -6468,7 +6468,7 @@
         <v>5</v>
       </c>
       <c r="C281" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E281" t="s">
         <v>17</v>
@@ -6486,7 +6486,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E282" t="s">
         <v>17</v>
@@ -6504,7 +6504,7 @@
         <v>5</v>
       </c>
       <c r="C283" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E283" t="s">
         <v>17</v>
@@ -6522,7 +6522,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E284" t="s">
         <v>17</v>
@@ -6537,10 +6537,10 @@
         <v>46176</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C285" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E285" t="s">
         <v>17</v>
@@ -6576,7 +6576,7 @@
         <v>5</v>
       </c>
       <c r="C287" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E287" t="s">
         <v>17</v>
@@ -6594,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E288" t="s">
         <v>17</v>
@@ -6612,7 +6612,7 @@
         <v>5</v>
       </c>
       <c r="C289" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E289" t="s">
         <v>17</v>
@@ -6630,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E290" t="s">
         <v>17</v>
@@ -6645,7 +6645,7 @@
         <v>46174</v>
       </c>
       <c r="B291" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C291" t="s">
         <v>12</v>
@@ -6663,10 +6663,10 @@
         <v>46174</v>
       </c>
       <c r="B292" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C292" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E292" t="s">
         <v>17</v>
@@ -6684,7 +6684,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E293" t="s">
         <v>17</v>
@@ -6702,7 +6702,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D294" t="s">
         <v>10</v>
@@ -6723,7 +6723,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D295" t="s">
         <v>24</v>
@@ -6759,10 +6759,10 @@
         <v>46174</v>
       </c>
       <c r="B297" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C297" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E297" t="s">
         <v>17</v>
@@ -6777,10 +6777,10 @@
         <v>46173</v>
       </c>
       <c r="B298" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C298" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E298" t="s">
         <v>17</v>
@@ -6795,7 +6795,7 @@
         <v>46173</v>
       </c>
       <c r="B299" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C299" t="s">
         <v>3</v>
@@ -6813,7 +6813,7 @@
         <v>46173</v>
       </c>
       <c r="B300" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C300" t="s">
         <v>13</v>
@@ -6831,7 +6831,7 @@
         <v>46173</v>
       </c>
       <c r="B301" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C301" t="s">
         <v>21</v>
@@ -6849,7 +6849,7 @@
         <v>46173</v>
       </c>
       <c r="B302" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C302" t="s">
         <v>3</v>
@@ -6868,7 +6868,7 @@
         <v>46173</v>
       </c>
       <c r="B303" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C303" t="s">
         <v>12</v>
@@ -6892,7 +6892,7 @@
         <v>13</v>
       </c>
       <c r="D304" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E304" t="s">
         <v>17</v>
@@ -6907,7 +6907,7 @@
         <v>46172</v>
       </c>
       <c r="B305" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C305" t="s">
         <v>13</v>
@@ -6925,10 +6925,10 @@
         <v>46172</v>
       </c>
       <c r="B306" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C306" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E306" t="s">
         <v>17</v>
@@ -6946,7 +6946,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E307" t="s">
         <v>17</v>
@@ -6961,10 +6961,10 @@
         <v>46171</v>
       </c>
       <c r="B308" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C308" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E308" t="s">
         <v>17</v>
@@ -6982,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E309" t="s">
         <v>17</v>
@@ -6997,7 +6997,7 @@
         <v>46171</v>
       </c>
       <c r="B310" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C310" t="s">
         <v>4</v>
@@ -7015,7 +7015,7 @@
         <v>46171</v>
       </c>
       <c r="B311" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C311" t="s">
         <v>9</v>
@@ -7033,13 +7033,13 @@
         <v>46170</v>
       </c>
       <c r="B312" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C312" t="s">
         <v>14</v>
       </c>
       <c r="D312" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E312" t="s">
         <v>17</v>
@@ -7075,13 +7075,13 @@
         <v>46169</v>
       </c>
       <c r="B314" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C314" t="s">
         <v>12</v>
       </c>
       <c r="E314" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F314" s="5">
         <v>290</v>
@@ -7099,7 +7099,7 @@
         <v>14</v>
       </c>
       <c r="D315" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E315" t="s">
         <v>17</v>
@@ -7114,7 +7114,7 @@
         <v>46169</v>
       </c>
       <c r="B316" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C316" t="s">
         <v>13</v>
@@ -7123,7 +7123,7 @@
         <v>30</v>
       </c>
       <c r="E316" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F316" s="5">
         <v>28</v>
@@ -7138,10 +7138,10 @@
         <v>5</v>
       </c>
       <c r="C317" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D317" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E317" t="s">
         <v>17</v>
@@ -7159,10 +7159,10 @@
         <v>16</v>
       </c>
       <c r="C318" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D318" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E318" t="s">
         <v>17</v>
@@ -7180,10 +7180,10 @@
         <v>16</v>
       </c>
       <c r="C319" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D319" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E319" t="s">
         <v>17</v>
@@ -7199,10 +7199,10 @@
         <v>16</v>
       </c>
       <c r="C320" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D320" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E320" t="s">
         <v>17</v>
@@ -7217,10 +7217,10 @@
         <v>46153</v>
       </c>
       <c r="B321" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C321" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E321" t="s">
         <v>17</v>
@@ -7238,7 +7238,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E322" t="s">
         <v>17</v>
@@ -7253,16 +7253,16 @@
         <v>46167</v>
       </c>
       <c r="B323" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C323" t="s">
         <v>13</v>
       </c>
       <c r="D323" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E323" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F323" s="5">
         <v>125</v>
@@ -7277,10 +7277,10 @@
         <v>16</v>
       </c>
       <c r="C324" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D324" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E324" t="s">
         <v>17</v>
@@ -7301,7 +7301,7 @@
         <v>9</v>
       </c>
       <c r="D325" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E325" t="s">
         <v>17</v>
@@ -7316,13 +7316,13 @@
         <v>46167</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C326" t="s">
         <v>13</v>
       </c>
       <c r="E326" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F326" s="5">
         <v>136.83000000000001</v>
@@ -7334,16 +7334,16 @@
         <v>46166</v>
       </c>
       <c r="B327" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C327" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D327" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E327" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F327" s="5">
         <v>260</v>
@@ -7355,16 +7355,16 @@
         <v>46166</v>
       </c>
       <c r="B328" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C328" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D328" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E328" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F328" s="5">
         <v>120</v>
@@ -7376,13 +7376,13 @@
         <v>46165</v>
       </c>
       <c r="B329" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C329" t="s">
         <v>13</v>
       </c>
       <c r="E329" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F329" s="5">
         <v>739.34</v>
@@ -7394,13 +7394,13 @@
         <v>46165</v>
       </c>
       <c r="B330" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C330" t="s">
         <v>12</v>
       </c>
       <c r="E330" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F330" s="5">
         <v>290</v>
@@ -7415,7 +7415,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D331" t="s">
         <v>27</v>
@@ -7438,7 +7438,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D332" t="s">
         <v>27</v>
@@ -7456,16 +7456,16 @@
         <v>46164</v>
       </c>
       <c r="B333" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C333" t="s">
         <v>3</v>
       </c>
       <c r="D333" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E333" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F333" s="5">
         <v>536</v>
@@ -7477,16 +7477,16 @@
         <v>46164</v>
       </c>
       <c r="B334" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C334" t="s">
         <v>3</v>
       </c>
       <c r="D334" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E334" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F334" s="5">
         <v>1122</v>
@@ -7498,16 +7498,16 @@
         <v>46163</v>
       </c>
       <c r="B335" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C335" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D335" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E335" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F335" s="5">
         <v>192</v>
@@ -7558,7 +7558,7 @@
         <v>46162</v>
       </c>
       <c r="B338" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C338" t="s">
         <v>13</v>
@@ -7567,7 +7567,7 @@
         <v>30</v>
       </c>
       <c r="E338" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F338" s="5">
         <v>56</v>
@@ -7579,13 +7579,13 @@
         <v>46161</v>
       </c>
       <c r="B339" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C339" t="s">
         <v>12</v>
       </c>
       <c r="E339" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F339" s="5">
         <v>290</v>
@@ -7597,7 +7597,7 @@
         <v>46161</v>
       </c>
       <c r="B340" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C340" t="s">
         <v>13</v>
@@ -7606,7 +7606,7 @@
         <v>30</v>
       </c>
       <c r="E340" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F340" s="5">
         <v>95</v>
@@ -7618,7 +7618,7 @@
         <v>46161</v>
       </c>
       <c r="B341" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C341" t="s">
         <v>13</v>
@@ -7627,7 +7627,7 @@
         <v>30</v>
       </c>
       <c r="E341" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F341" s="5">
         <v>90</v>
@@ -7642,10 +7642,10 @@
         <v>19</v>
       </c>
       <c r="C342" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D342" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E342" t="s">
         <v>19</v>
@@ -7663,10 +7663,10 @@
         <v>19</v>
       </c>
       <c r="C343" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D343" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E343" t="s">
         <v>19</v>
@@ -7684,10 +7684,10 @@
         <v>16</v>
       </c>
       <c r="C344" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D344" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E344" t="s">
         <v>19</v>
@@ -7702,16 +7702,16 @@
         <v>46160</v>
       </c>
       <c r="B345" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C345" t="s">
         <v>13</v>
       </c>
       <c r="D345" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E345" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F345" s="5">
         <v>192</v>
@@ -7723,16 +7723,16 @@
         <v>46160</v>
       </c>
       <c r="B346" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C346" t="s">
         <v>13</v>
       </c>
       <c r="D346" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E346" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F346" s="5">
         <v>690</v>
@@ -7744,13 +7744,13 @@
         <v>46158</v>
       </c>
       <c r="B347" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C347" t="s">
         <v>21</v>
       </c>
       <c r="E347" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F347" s="5">
         <v>3600</v>
@@ -7762,16 +7762,16 @@
         <v>46158</v>
       </c>
       <c r="B348" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C348" t="s">
         <v>13</v>
       </c>
       <c r="D348" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E348" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F348" s="5">
         <v>659</v>
@@ -7786,7 +7786,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E349" t="s">
         <v>17</v>
@@ -7801,13 +7801,13 @@
         <v>46156</v>
       </c>
       <c r="B350" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C350" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D350" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E350" t="s">
         <v>20</v>
@@ -7822,13 +7822,13 @@
         <v>46156</v>
       </c>
       <c r="B351" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C351" t="s">
         <v>4</v>
       </c>
       <c r="D351" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E351" t="s">
         <v>20</v>
@@ -7849,7 +7849,7 @@
         <v>4</v>
       </c>
       <c r="D352" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E352" t="s">
         <v>20</v>
@@ -7864,13 +7864,13 @@
         <v>46156</v>
       </c>
       <c r="B353" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C353" t="s">
         <v>12</v>
       </c>
       <c r="E353" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F353" s="5">
         <v>300</v>
@@ -7882,10 +7882,10 @@
         <v>46154</v>
       </c>
       <c r="B354" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C354" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="F354" s="5">
         <v>1830</v>
@@ -7897,7 +7897,7 @@
         <v>46154</v>
       </c>
       <c r="B355" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C355" t="s">
         <v>9</v>
@@ -7912,16 +7912,16 @@
         <v>46154</v>
       </c>
       <c r="B356" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C356" t="s">
         <v>9</v>
       </c>
       <c r="D356" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E356" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F356" s="5">
         <v>2440</v>
@@ -7933,7 +7933,7 @@
         <v>46153</v>
       </c>
       <c r="C357" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E357" t="s">
         <v>17</v>
@@ -7948,10 +7948,10 @@
         <v>46153</v>
       </c>
       <c r="B358" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C358" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E358" t="s">
         <v>17</v>
@@ -7969,7 +7969,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E359" t="s">
         <v>17</v>
@@ -7987,7 +7987,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E360" t="s">
         <v>20</v>
@@ -8002,13 +8002,13 @@
         <v>46153</v>
       </c>
       <c r="B361" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C361" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D361" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E361" t="s">
         <v>20</v>
@@ -8026,10 +8026,10 @@
         <v>16</v>
       </c>
       <c r="C362" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D362" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E362" t="s">
         <v>17</v>
@@ -8044,13 +8044,13 @@
         <v>46153</v>
       </c>
       <c r="B363" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C363" t="s">
         <v>3</v>
       </c>
       <c r="E363" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F363" s="5">
         <v>2768</v>
@@ -8065,10 +8065,10 @@
         <v>16</v>
       </c>
       <c r="C364" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D364" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E364" t="s">
         <v>17</v>
@@ -8083,10 +8083,10 @@
         <v>46152</v>
       </c>
       <c r="B365" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C365" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E365" t="s">
         <v>17</v>
@@ -8104,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E366" t="s">
         <v>17</v>
@@ -8119,13 +8119,13 @@
         <v>46152</v>
       </c>
       <c r="B367" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C367" t="s">
         <v>12</v>
       </c>
       <c r="E367" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F367" s="5">
         <v>300</v>
@@ -8143,7 +8143,7 @@
         <v>4</v>
       </c>
       <c r="D368" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E368" t="s">
         <v>20</v>
@@ -8161,10 +8161,10 @@
         <v>16</v>
       </c>
       <c r="C369" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D369" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E369" t="s">
         <v>20</v>
@@ -8179,13 +8179,13 @@
         <v>46152</v>
       </c>
       <c r="B370" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C370" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D370" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E370" t="s">
         <v>20</v>
@@ -8206,7 +8206,7 @@
         <v>4</v>
       </c>
       <c r="D371" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E371" t="s">
         <v>20</v>
@@ -8224,7 +8224,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D372" t="s">
         <v>8</v>
@@ -8242,10 +8242,10 @@
         <v>46151</v>
       </c>
       <c r="B373" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C373" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E373" t="s">
         <v>17</v>
@@ -8263,7 +8263,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E374" t="s">
         <v>17</v>
@@ -8278,7 +8278,7 @@
         <v>46151</v>
       </c>
       <c r="B375" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C375" t="s">
         <v>3</v>
@@ -8296,7 +8296,7 @@
         <v>46151</v>
       </c>
       <c r="B376" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C376" t="s">
         <v>3</v>
@@ -8317,10 +8317,10 @@
         <v>6</v>
       </c>
       <c r="C377" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D377" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E377" t="s">
         <v>17</v>
@@ -8338,7 +8338,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E378" t="s">
         <v>17</v>
@@ -8356,10 +8356,10 @@
         <v>16</v>
       </c>
       <c r="C379" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D379" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E379" t="s">
         <v>17</v>
@@ -8374,13 +8374,13 @@
         <v>46150</v>
       </c>
       <c r="B380" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C380" t="s">
         <v>12</v>
       </c>
       <c r="E380" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F380" s="5">
         <v>292.89999999999998</v>
@@ -8392,10 +8392,10 @@
         <v>46150</v>
       </c>
       <c r="B381" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C381" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E381" t="s">
         <v>17</v>
@@ -8410,10 +8410,10 @@
         <v>46150</v>
       </c>
       <c r="B382" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C382" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E382" t="s">
         <v>17</v>
@@ -8431,10 +8431,10 @@
         <v>6</v>
       </c>
       <c r="C383" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D383" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E383" t="s">
         <v>17</v>
@@ -8452,7 +8452,7 @@
         <v>16</v>
       </c>
       <c r="C384" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E384" t="s">
         <v>17</v>
@@ -8470,10 +8470,10 @@
         <v>16</v>
       </c>
       <c r="C385" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D385" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E385" t="s">
         <v>17</v>
@@ -8509,10 +8509,10 @@
         <v>16</v>
       </c>
       <c r="C387" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D387" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E387" t="s">
         <v>17</v>
@@ -8527,10 +8527,10 @@
         <v>46147</v>
       </c>
       <c r="B388" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C388" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E388" t="s">
         <v>17</v>
@@ -8548,7 +8548,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E389" t="s">
         <v>17</v>
@@ -8563,13 +8563,13 @@
         <v>46147</v>
       </c>
       <c r="B390" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C390" t="s">
         <v>9</v>
       </c>
       <c r="D390" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E390" t="s">
         <v>17</v>
@@ -8584,16 +8584,16 @@
         <v>46147</v>
       </c>
       <c r="B391" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C391" t="s">
         <v>13</v>
       </c>
       <c r="D391" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E391" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F391" s="5">
         <v>294</v>
@@ -8608,7 +8608,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E392" t="s">
         <v>17</v>
@@ -8626,7 +8626,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E393" t="s">
         <v>17</v>
@@ -8641,10 +8641,10 @@
         <v>46146</v>
       </c>
       <c r="B394" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C394" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E394" t="s">
         <v>17</v>
@@ -8659,10 +8659,10 @@
         <v>46360</v>
       </c>
       <c r="B395" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C395" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E395" t="s">
         <v>17</v>
@@ -8677,10 +8677,10 @@
         <v>46146</v>
       </c>
       <c r="B396" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C396" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E396" t="s">
         <v>17</v>
@@ -8695,10 +8695,10 @@
         <v>46146</v>
       </c>
       <c r="B397" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C397" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E397" t="s">
         <v>17</v>
@@ -8716,7 +8716,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E398" t="s">
         <v>17</v>
@@ -8734,7 +8734,7 @@
         <v>5</v>
       </c>
       <c r="C399" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E399" t="s">
         <v>17</v>
@@ -8752,7 +8752,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E400" t="s">
         <v>17</v>
@@ -8770,7 +8770,7 @@
         <v>5</v>
       </c>
       <c r="C401" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E401" t="s">
         <v>17</v>
@@ -8788,7 +8788,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E402" t="s">
         <v>17</v>
@@ -8809,7 +8809,7 @@
         <v>9</v>
       </c>
       <c r="D403" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E403" t="s">
         <v>17</v>
@@ -8827,7 +8827,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D404" t="s">
         <v>8</v>
@@ -8848,7 +8848,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -8869,7 +8869,7 @@
         <v>5</v>
       </c>
       <c r="C406" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E406" t="s">
         <v>17</v>
@@ -8887,7 +8887,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E407" t="s">
         <v>17</v>
@@ -8905,7 +8905,7 @@
         <v>5</v>
       </c>
       <c r="C408" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E408" t="s">
         <v>17</v>
@@ -8923,7 +8923,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E409" t="s">
         <v>17</v>
@@ -8938,10 +8938,10 @@
         <v>46143</v>
       </c>
       <c r="B410" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C410" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D410" t="s">
         <v>22</v>
@@ -8962,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E411" t="s">
         <v>17</v>
@@ -8983,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="D412" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E412" t="s">
         <v>17</v>
@@ -9004,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E413" t="s">
         <v>17</v>
@@ -9025,7 +9025,7 @@
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E414" t="s">
         <v>17</v>
@@ -9040,10 +9040,10 @@
         <v>46143</v>
       </c>
       <c r="B415" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C415" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E415" t="s">
         <v>17</v>
@@ -9061,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E416" t="s">
         <v>17</v>
@@ -9079,7 +9079,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D417" t="s">
         <v>10</v>
@@ -9100,7 +9100,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E418" t="s">
         <v>17</v>
@@ -9133,10 +9133,10 @@
         <v>46142</v>
       </c>
       <c r="B420" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C420" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E420" t="s">
         <v>17</v>
@@ -9151,16 +9151,16 @@
         <v>46142</v>
       </c>
       <c r="B421" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C421" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="D421" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E421" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F421" s="5"/>
       <c r="G421" s="5">
@@ -9175,13 +9175,13 @@
         <v>16</v>
       </c>
       <c r="C422" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="D422" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E422" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F422" s="5">
         <v>45221</v>
@@ -9193,16 +9193,16 @@
         <v>46142</v>
       </c>
       <c r="B423" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C423" t="s">
         <v>9</v>
       </c>
       <c r="D423" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E423" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F423" s="5">
         <v>450</v>
@@ -9217,7 +9217,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F424" s="5"/>
       <c r="G424" s="5">
@@ -9229,13 +9229,13 @@
         <v>46142</v>
       </c>
       <c r="B425" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C425" t="s">
         <v>9</v>
       </c>
       <c r="D425" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E425" t="s">
         <v>19</v>
@@ -9250,13 +9250,13 @@
         <v>46142</v>
       </c>
       <c r="B426" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C426" t="s">
         <v>9</v>
       </c>
       <c r="D426" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E426" t="s">
         <v>19</v>
@@ -9271,13 +9271,13 @@
         <v>46142</v>
       </c>
       <c r="B427" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C427" t="s">
         <v>9</v>
       </c>
       <c r="D427" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E427" t="s">
         <v>19</v>
@@ -9292,13 +9292,13 @@
         <v>46142</v>
       </c>
       <c r="B428" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C428" t="s">
         <v>9</v>
       </c>
       <c r="D428" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E428" t="s">
         <v>19</v>
@@ -9313,13 +9313,13 @@
         <v>46142</v>
       </c>
       <c r="B429" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C429" t="s">
         <v>9</v>
       </c>
       <c r="D429" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E429" t="s">
         <v>19</v>
@@ -9334,13 +9334,13 @@
         <v>46142</v>
       </c>
       <c r="B430" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C430" t="s">
         <v>9</v>
       </c>
       <c r="D430" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E430" t="s">
         <v>19</v>
@@ -9355,13 +9355,13 @@
         <v>46141</v>
       </c>
       <c r="B431" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C431" t="s">
         <v>9</v>
       </c>
       <c r="D431" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E431" t="s">
         <v>19</v>
@@ -9376,16 +9376,16 @@
         <v>46141</v>
       </c>
       <c r="B432" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C432" t="s">
         <v>9</v>
       </c>
       <c r="D432" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E432" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F432" s="5">
         <v>880</v>
@@ -9397,13 +9397,13 @@
         <v>46140</v>
       </c>
       <c r="B433" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C433" t="s">
         <v>9</v>
       </c>
       <c r="D433" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E433" t="s">
         <v>19</v>
@@ -9418,16 +9418,16 @@
         <v>46140</v>
       </c>
       <c r="B434" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C434" t="s">
         <v>14</v>
       </c>
       <c r="D434" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E434" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F434" s="5">
         <v>589</v>
@@ -9439,13 +9439,13 @@
         <v>46139</v>
       </c>
       <c r="B435" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C435" t="s">
         <v>9</v>
       </c>
       <c r="D435" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E435" t="s">
         <v>19</v>
@@ -9460,13 +9460,13 @@
         <v>46138</v>
       </c>
       <c r="B436" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C436" t="s">
         <v>9</v>
       </c>
       <c r="D436" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E436" t="s">
         <v>19</v>
@@ -9481,13 +9481,13 @@
         <v>46138</v>
       </c>
       <c r="B437" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C437" t="s">
         <v>9</v>
       </c>
       <c r="D437" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E437" t="s">
         <v>19</v>
@@ -9502,7 +9502,7 @@
         <v>46138</v>
       </c>
       <c r="B438" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C438" t="s">
         <v>9</v>
@@ -9523,13 +9523,13 @@
         <v>46138</v>
       </c>
       <c r="B439" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C439" t="s">
         <v>9</v>
       </c>
       <c r="D439" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E439" t="s">
         <v>19</v>
@@ -9544,13 +9544,13 @@
         <v>46138</v>
       </c>
       <c r="B440" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C440" t="s">
         <v>9</v>
       </c>
       <c r="D440" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E440" t="s">
         <v>19</v>
@@ -9565,13 +9565,13 @@
         <v>46137</v>
       </c>
       <c r="B441" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C441" t="s">
         <v>9</v>
       </c>
       <c r="D441" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E441" t="s">
         <v>19</v>
@@ -9592,7 +9592,7 @@
         <v>9</v>
       </c>
       <c r="D442" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E442" t="s">
         <v>19</v>
@@ -9610,7 +9610,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E443" t="s">
         <v>17</v>
@@ -9625,16 +9625,16 @@
         <v>46134</v>
       </c>
       <c r="B444" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C444" t="s">
         <v>3</v>
       </c>
       <c r="D444" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E444" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F444" s="5">
         <v>308</v>
@@ -9646,16 +9646,16 @@
         <v>46131</v>
       </c>
       <c r="B445" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C445" t="s">
         <v>11</v>
       </c>
       <c r="D445" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E445" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F445" s="5">
         <v>1495</v>
@@ -9667,13 +9667,13 @@
         <v>46130</v>
       </c>
       <c r="B446" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C446" t="s">
         <v>13</v>
       </c>
       <c r="E446" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F446" s="5">
         <v>992</v>
@@ -9685,16 +9685,16 @@
         <v>46130</v>
       </c>
       <c r="B447" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C447" t="s">
         <v>11</v>
       </c>
       <c r="D447" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E447" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F447" s="5">
         <v>1148</v>
@@ -9706,13 +9706,13 @@
         <v>46128</v>
       </c>
       <c r="B448" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C448" t="s">
         <v>12</v>
       </c>
       <c r="E448" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F448" s="5">
         <v>290</v>
@@ -9724,13 +9724,13 @@
         <v>46127</v>
       </c>
       <c r="B449" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C449" t="s">
         <v>13</v>
       </c>
       <c r="E449" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F449" s="5">
         <v>28</v>
@@ -9742,10 +9742,10 @@
         <v>46127</v>
       </c>
       <c r="B450" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C450" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E450" t="s">
         <v>17</v>
@@ -9763,7 +9763,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E451" t="s">
         <v>17</v>
@@ -9781,7 +9781,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D452" t="s">
         <v>8</v>
@@ -9802,7 +9802,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E453" t="s">
         <v>17</v>
@@ -9820,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D454" t="s">
         <v>10</v>
@@ -9838,10 +9838,10 @@
         <v>46126</v>
       </c>
       <c r="B455" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C455" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E455" t="s">
         <v>17</v>
@@ -9859,7 +9859,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E456" t="s">
         <v>17</v>
@@ -9874,10 +9874,10 @@
         <v>46126</v>
       </c>
       <c r="B457" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C457" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E457" t="s">
         <v>17</v>
@@ -9895,7 +9895,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E458" t="s">
         <v>17</v>
@@ -9913,7 +9913,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E459" t="s">
         <v>17</v>
@@ -9928,10 +9928,10 @@
         <v>46125</v>
       </c>
       <c r="B460" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C460" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E460" t="s">
         <v>17</v>
@@ -9949,7 +9949,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E461" t="s">
         <v>17</v>
@@ -9964,16 +9964,16 @@
         <v>46125</v>
       </c>
       <c r="B462" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C462" t="s">
         <v>13</v>
       </c>
       <c r="D462" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E462" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F462" s="5">
         <v>234</v>
@@ -9992,13 +9992,13 @@
         <v>46124</v>
       </c>
       <c r="B464" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C464" t="s">
         <v>12</v>
       </c>
       <c r="E464" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F464" s="5">
         <v>290</v>
@@ -10010,13 +10010,13 @@
         <v>46123</v>
       </c>
       <c r="B465" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C465" t="s">
         <v>3</v>
       </c>
       <c r="E465" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F465" s="5">
         <v>556</v>
@@ -10031,10 +10031,10 @@
         <v>16</v>
       </c>
       <c r="C466" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D466" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E466" t="s">
         <v>17</v>
@@ -10049,10 +10049,10 @@
         <v>46122</v>
       </c>
       <c r="B467" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C467" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E467" t="s">
         <v>17</v>
@@ -10070,7 +10070,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E468" t="s">
         <v>17</v>
@@ -10085,10 +10085,10 @@
         <v>46121</v>
       </c>
       <c r="B469" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C469" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E469" t="s">
         <v>17</v>
@@ -10106,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E470" t="s">
         <v>17</v>
@@ -10121,10 +10121,10 @@
         <v>46121</v>
       </c>
       <c r="B471" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C471" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E471" t="s">
         <v>17</v>
@@ -10142,7 +10142,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E472" t="s">
         <v>17</v>
@@ -10160,10 +10160,10 @@
         <v>6</v>
       </c>
       <c r="C473" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D473" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E473" t="s">
         <v>17</v>
@@ -10181,7 +10181,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E474" t="s">
         <v>17</v>
@@ -10199,10 +10199,10 @@
         <v>16</v>
       </c>
       <c r="C475" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D475" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E475" t="s">
         <v>17</v>
@@ -10217,13 +10217,13 @@
         <v>46120</v>
       </c>
       <c r="B476" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C476" t="s">
         <v>12</v>
       </c>
       <c r="E476" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F476" s="5">
         <v>290</v>
@@ -10235,10 +10235,10 @@
         <v>46120</v>
       </c>
       <c r="B477" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C477" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E477" t="s">
         <v>17</v>
@@ -10253,13 +10253,13 @@
         <v>46120</v>
       </c>
       <c r="B478" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C478" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E478" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F478" s="5">
         <v>8500</v>
@@ -10274,10 +10274,10 @@
         <v>6</v>
       </c>
       <c r="C479" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D479" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E479" t="s">
         <v>17</v>
@@ -10295,10 +10295,10 @@
         <v>16</v>
       </c>
       <c r="C480" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D480" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E480" t="s">
         <v>17</v>
@@ -10316,10 +10316,10 @@
         <v>16</v>
       </c>
       <c r="C481" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D481" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E481" t="s">
         <v>17</v>
@@ -10334,13 +10334,13 @@
         <v>46119</v>
       </c>
       <c r="B482" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C482" t="s">
         <v>13</v>
       </c>
       <c r="E482" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F482" s="5">
         <v>56</v>
@@ -10355,7 +10355,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D483" t="s">
         <v>8</v>
@@ -10376,10 +10376,10 @@
         <v>16</v>
       </c>
       <c r="C484" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D484" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E484" t="s">
         <v>17</v>
@@ -10415,7 +10415,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D486" t="s">
         <v>8</v>
@@ -10433,10 +10433,10 @@
         <v>46117</v>
       </c>
       <c r="B487" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C487" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E487" t="s">
         <v>17</v>
@@ -10448,13 +10448,13 @@
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A488" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B488" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C488" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F488" s="5">
         <v>5000</v>
@@ -10471,7 +10471,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E489" t="s">
         <v>17</v>
@@ -10489,7 +10489,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E490" t="s">
         <v>17</v>
@@ -10504,13 +10504,13 @@
         <v>46117</v>
       </c>
       <c r="B491" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C491" t="s">
         <v>12</v>
       </c>
       <c r="E491" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F491" s="5">
         <v>290</v>
@@ -10522,10 +10522,10 @@
         <v>46116</v>
       </c>
       <c r="B492" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C492" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E492" t="s">
         <v>17</v>
@@ -10540,13 +10540,13 @@
         <v>46116</v>
       </c>
       <c r="B493" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C493" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E493" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F493" s="5">
         <v>10596</v>
@@ -10561,7 +10561,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E494" t="s">
         <v>17</v>
@@ -10579,7 +10579,7 @@
         <v>5</v>
       </c>
       <c r="C495" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E495" t="s">
         <v>17</v>
@@ -10597,7 +10597,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E496" t="s">
         <v>17</v>
@@ -10615,7 +10615,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D497" t="s">
         <v>10</v>
@@ -10636,7 +10636,7 @@
         <v>5</v>
       </c>
       <c r="C498" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E498" t="s">
         <v>17</v>
@@ -10654,7 +10654,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E499" t="s">
         <v>17</v>
@@ -10669,16 +10669,16 @@
         <v>46115</v>
       </c>
       <c r="B500" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C500" t="s">
         <v>11</v>
       </c>
       <c r="D500" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E500" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F500" s="5">
         <v>1047</v>
@@ -10690,10 +10690,10 @@
         <v>46115</v>
       </c>
       <c r="B501" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C501" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E501" t="s">
         <v>17</v>
@@ -10711,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E502" t="s">
         <v>17</v>
@@ -10729,10 +10729,10 @@
         <v>15</v>
       </c>
       <c r="C503" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D503" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E503" t="s">
         <v>17</v>
@@ -10747,16 +10747,16 @@
         <v>46114</v>
       </c>
       <c r="B504" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C504" t="s">
         <v>3</v>
       </c>
       <c r="D504" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E504" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F504" s="5">
         <v>569</v>
@@ -10771,7 +10771,7 @@
         <v>5</v>
       </c>
       <c r="C505" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E505" t="s">
         <v>17</v>
@@ -10789,7 +10789,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E506" t="s">
         <v>17</v>
@@ -10804,13 +10804,13 @@
         <v>46114</v>
       </c>
       <c r="B507" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C507" t="s">
         <v>13</v>
       </c>
       <c r="E507" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F507" s="5">
         <v>76</v>
@@ -10822,10 +10822,10 @@
         <v>46113</v>
       </c>
       <c r="B508" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C508" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E508" t="s">
         <v>17</v>
@@ -10843,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E509" t="s">
         <v>17</v>
@@ -10861,7 +10861,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D510" t="s">
         <v>10</v>
@@ -10882,7 +10882,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="D511" t="s">
         <v>10</v>
@@ -10903,7 +10903,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E512" t="s">
         <v>17</v>
@@ -10954,7 +10954,7 @@
         <v>46113</v>
       </c>
       <c r="B515" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C515" t="s">
         <v>9</v>
@@ -10978,7 +10978,7 @@
         <v>9</v>
       </c>
       <c r="D516" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E516" t="s">
         <v>19</v>
@@ -10999,7 +10999,7 @@
         <v>4</v>
       </c>
       <c r="D517" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E517" t="s">
         <v>19</v>
@@ -11102,7 +11102,7 @@
     <row r="564" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="7">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B518:B568" xr:uid="{088A77D5-7E8F-4BBB-BC6E-3BA1D0FE9318}">
       <formula1>"'Personal Info'!$M$2:$M$20"</formula1>
     </dataValidation>
@@ -11113,9 +11113,6 @@
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Payment Mode" error="Please select a payment mode from the dropdown list or add a new one in Personal Info sheet." sqref="E569:E612" xr:uid="{3C65265B-99AE-4FBE-ABA8-BBD0C21C97EA}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C316 C408 C401 C500:C501 C507:C517 C497:C498 C494:C495 C503:C505 C319:C321 C360:C365 C367:C373 C375:C381 C479:C488 C490:C492 C410:C460 C403:C406 C469:C471 C473:C477 C383:C388 C390:C394 C397 C462:C467 C399 C323:C358 B2:B517" xr:uid="{49E83C0A-1F87-4ECF-AAFD-1C44CDF48133}">
       <formula1>#REF!</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Category" error="Please select a category from the dropdown list or add a new one in Personal Info sheet." sqref="C569:C612" xr:uid="{2346808E-CF5F-4237-A4F7-AE68FAE09BDD}">
